--- a/stories/arbres/ATOM-SOC.TRA.001-02.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léa tient la main de maman. Elles vont au port. Elles restent avec un adulte. Maman, c'est l'adulte. Un bateau arrive. Le bateau fait une sirène douce. L'eau clapote. Maman dit : c'est un bateau. C'est le nom du véhicule. Léa répète : un bateau. Elles montent avec maman. Léa s'assoit près de maman. Le bateau glisse. Dans le ciel, un avion passe. L'avion fait un trait blanc. Maman dit : c'est un avion. Léa dit : un avion. Sur l'autre rive, un train roule. Le train fait tchou tchou. Maman dit : c'est un train. Léa dit : un train. Train, avion, bateau. Léa nomme. Elle reste avec maman. Parce qu'elle reste avec un adulte, le voyage est calme.</t>
+          <t>Léa tient la main de maman. Elles vont au port. Elles restent avec un adulte. Maman, c'est l'adulte. Un bateau arrive. Le bateau fait une sirène douce. L'eau clapote. C'est un bateau. C'est le nom du véhicule. Léa répète : un bateau. Elles montent avec maman. Léa s'assoit près de maman. Le bateau glisse. Dans le ciel, un avion passe. L'avion fait un trait blanc. C'est un avion. Un avion. Sur l'autre rive, un train roule. Le train fait tchou tchou. C'est un train. Un train. Train, avion, bateau. Léa nomme. Elle reste avec maman. Parce qu'elle reste avec un adulte, le voyage est calme.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,19 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Léa tient la main de maman. Elles vont au port. Elles restent avec un adulte. Maman, c'est l'adulte. Un bateau arrive. Le bateau fait une sirène douce. L'eau clapote.
+maman|C'est un bateau. C'est le nom du véhicule.
+narrateur|Léa répète : un bateau. Elles montent avec maman. Léa s'assoit près de maman. Le bateau glisse. Dans le ciel, un avion passe. L'avion fait un trait blanc.
+maman|C'est un avion.
+enfant-f|Un avion. Sur l'autre rive, un train roule.
+narrateur|Le train fait tchou tchou.
+maman|C'est un train.
+enfant-f|Un train. Train, avion, bateau.
+narrateur|Léa nomme. Elle reste avec maman. Parce qu'elle reste avec un adulte, le voyage est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1498,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Léa nomme un véhicule. Lequel ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a dit le nom du véhicule. Bateau. Avion. Train. Elle est restée avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1838,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le bateau s'arrête. Léa donne la main à maman. Elles descendent ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2005,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2045,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.TRA.001-02.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1318,6 +1323,11 @@
 narrateur|Léa nomme. Elle reste avec maman. Parce qu'elle reste avec un adulte, le voyage est calme.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1505,6 +1515,7 @@
           <t>narrateur|Léa nomme un véhicule. Lequel ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1687,7 @@
           <t>narrateur|Léa a dit le nom du véhicule. Bateau. Avion. Train. Elle est restée avec maman.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1843,6 +1855,7 @@
           <t>narrateur|Le bateau s'arrête. Léa donne la main à maman. Elles descendent ensemble.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2010,6 +2023,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2028,7 +2042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2052,6 +2066,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2253,6 +2281,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.TRA.001-02.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le bateau de Léa</t>
+          <t>Le bac de Victorino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Victorino veut voir la maison rouge de l'autre rive, en bac avec maman. Le banc est mouillé. Ils s'assoient au sec. Le bac glisse. La maison arrive.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léa tient la main de maman. Elles vont au port. Elles restent avec un adulte. Maman, c'est l'adulte. Un bateau arrive. Le bateau fait une sirène douce. L'eau clapote. C'est un bateau. C'est le nom du véhicule. Léa répète : un bateau. Elles montent avec maman. Léa s'assoit près de maman. Le bateau glisse. Dans le ciel, un avion passe. L'avion fait un trait blanc. C'est un avion. Un avion. Sur l'autre rive, un train roule. Le train fait tchou tchou. C'est un train. Un train. Train, avion, bateau. Léa nomme. Elle reste avec maman. Parce qu'elle reste avec un adulte, le voyage est calme.</t>
+          <t>Les cordes du bac sentent l'eau salée. Le ponton mouillé brille par plaques. Une mouette crie, tout près. Le petit bac attend, tout bas. Victorino vit ici, avec maman. Tu as vu le bac, Victorino ? Il est petit. Oui. C'est un bateau. En ce moment, ils donnent la main. Ils montent sur le bac ensemble. Je veux la maison rouge. Sur l'autre rive. On la verra en glissant. On reste avec maman. Le banc du bac est mouillé. Une flaque tient au milieu. Il est mouillé ! On s'assoit sur le bord sec. Ici, près de moi. Victorino s'assoit contre maman. Le bois sec est rêche. Je reste. Oui. Assis, avec un adulte. Une corde tombe dans l'eau. Le bac se détache du ponton. On part ! On reste assis. L'eau clapote sous le plancher. Victorino tient la manche de maman. Ça bouge. Le bateau glisse. Toi, tu restes. Une petite vague lèche le bord. Des gouttes sautent sur la chaussure. Ma chaussure ! Elle va sécher. On ne se lève pas. Victorino garde les pieds au bois. Au loin, un toit rouge apparaît. La maison ! Bientôt. Le bac tourne un peu. La maison se cache, puis revient.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Léa tient la main de maman. Elles vont au port. Elles restent avec un adulte. Maman, c'est l'adulte. Un bateau arrive. Le bateau fait une sirène douce. L'eau clapote. Maman dit : c'est un bateau. C'est le &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt; du véhicule. Léa répète : un bateau. Elles montent avec maman. Léa s'assoit près de maman. Le bateau glisse. Dans le ciel, un avion passe. L'avion fait un trait blanc. Maman dit : c'est un avion. Léa dit : un avion. Sur l'autre rive, un train roule. Le train fait tchou tchou. Maman dit : c'est un train. Léa dit : un train. Train, avion, bateau. Léa nomme. Elle reste avec maman. Parce qu'elle reste avec un adulte, le voyage est calme.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les cordes du bac sentent l'eau salée. Le ponton mouillé brille par plaques. Une mouette crie, tout près. Le petit bac attend, tout bas. Victorino vit ici, avec maman. Tu as vu le bac, Victorino ? Il est petit. Oui. C'est un bateau. En ce moment, ils donnent la main. Ils montent sur le bac ensemble. Je veux la maison rouge. Sur l'autre rive. On la verra en glissant. On reste avec maman. Le banc du bac est mouillé. Une flaque tient au milieu. Il est mouillé ! On s'assoit sur le bord sec. Ici, près de moi. Victorino s'assoit contre maman. Le bois sec est rêche. Je reste. Oui. Assis, avec un adulte. Une corde tombe dans l'eau. Le bac se détache du ponton. On part ! On reste assis. L'eau clapote sous le plancher. Victorino tient la manche de maman. Ça bouge. Le bateau glisse. Toi, tu restes. Une petite vague lèche le bord. Des gouttes sautent sur la chaussure. Ma chaussure ! Elle va sécher. On ne se lève pas. Victorino garde les pieds au bois. Au loin, un toit rouge apparaît. La maison ! Bientôt. Le bac tourne un peu. La maison se cache, puis revient.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,15 +1324,51 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Léa tient la main de maman. Elles vont au port. Elles restent avec un adulte. Maman, c'est l'adulte. Un bateau arrive. Le bateau fait une sirène douce. L'eau clapote.
-maman|C'est un bateau. C'est le nom du véhicule.
-narrateur|Léa répète : un bateau. Elles montent avec maman. Léa s'assoit près de maman. Le bateau glisse. Dans le ciel, un avion passe. L'avion fait un trait blanc.
-maman|C'est un avion.
-enfant-f|Un avion. Sur l'autre rive, un train roule.
-narrateur|Le train fait tchou tchou.
-maman|C'est un train.
-enfant-f|Un train. Train, avion, bateau.
-narrateur|Léa nomme. Elle reste avec maman. Parce qu'elle reste avec un adulte, le voyage est calme.</t>
+          <t>narrateur|Les cordes du bac sentent l'eau salée.
+narrateur|Le ponton mouillé brille par plaques.
+narrateur|Une mouette crie, tout près.
+narrateur|Le petit bac attend, tout bas.
+narrateur|Victorino vit ici, avec maman.
+maman|Tu as vu le bac, Victorino ?
+enfant-m|Il est petit.
+maman|Oui.
+maman|C'est un bateau.
+narrateur|En ce moment, ils donnent la main.
+narrateur|Ils montent sur le bac ensemble.
+enfant-m|Je veux la maison rouge.
+enfant-m|Sur l'autre rive.
+maman|On la verra en glissant.
+maman|On reste avec maman.
+narrateur|Le banc du bac est mouillé.
+narrateur|Une flaque tient au milieu.
+enfant-m|Il est mouillé !
+maman|On s'assoit sur le bord sec.
+maman|Ici, près de moi.
+narrateur|Victorino s'assoit contre maman.
+narrateur|Le bois sec est rêche.
+enfant-m|Je reste.
+maman|Oui.
+maman|Assis, avec un adulte.
+narrateur|Une corde tombe dans l'eau.
+narrateur|Le bac se détache du ponton.
+enfant-m|On part !
+maman|On reste assis.
+narrateur|L'eau clapote sous le plancher.
+narrateur|Victorino tient la manche de maman.
+enfant-m|Ça bouge.
+maman|Le bateau glisse.
+maman|Toi, tu restes.
+narrateur|Une petite vague lèche le bord.
+narrateur|Des gouttes sautent sur la chaussure.
+enfant-m|Ma chaussure !
+maman|Elle va sécher.
+maman|On ne se lève pas.
+narrateur|Victorino garde les pieds au bois.
+narrateur|Au loin, un toit rouge apparaît.
+enfant-m|La maison !
+maman|Bientôt.
+narrateur|Le bac tourne un peu.
+narrateur|La maison se cache, puis revient.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1352,12 +1400,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Léa nomme un véhicule. Lequel ?</t>
+          <t>Victorino glisse sur l'eau. Quel véhicule le porte ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Léa &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;me un véhicule. Lequel ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino glisse sur l'eau. Quel véhicule le porte ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1367,12 +1415,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>bateau</t>
+          <t>le bateau</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>bateau | avion | train | un bateau | le bateau</t>
+          <t>bateau | le bateau | un bateau | bac | le bac</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1387,7 +1435,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle a vu un bateau. Quel véhicule ?</t>
+          <t>C'est le bateau. Quel véhicule le porte ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1436,7 +1484,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1512,10 +1560,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Léa nomme un véhicule. Lequel ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Victorino glisse sur l'eau.
+narrateur|Quel véhicule le porte ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1540,12 +1588,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Léa a dit le nom du véhicule. Bateau. Avion. Train. Elle est restée avec maman.</t>
+          <t>Le bateau. Le bac. Oui, le bateau. Ils restent assis sur le bord sec. La maison rouge grossit. Je la vois bien. Tu l'as voulue. La voilà. Une mouette suit le bac. Son ombre passe sur l'eau. Elle vole avec nous. Nous, on reste assis. Merci, Victorino. Le ponton de l'autre rive s'approche. Une corde attend, déjà. On arrive. On se lève avec maman. Quand le bac est arrêté. Le bois donne un petit choc. L'eau se calme contre le ponton. Il ne bouge plus. Maintenant on peut descendre.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Léa a dit le &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt; du véhicule. Bateau. Avion. Train. Elle est restée avec maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le bateau. Le bac. Oui, le bateau. Ils restent assis sur le bord sec. La maison rouge grossit. Je la vois bien. Tu l'as voulue. La voilà. Une mouette suit le bac. Son ombre passe sur l'eau. Elle vole avec nous. Nous, on reste assis. Merci, Victorino. Le ponton de l'autre rive s'approche. Une corde attend, déjà. On arrive. On se lève avec maman. Quand le bac est arrêté. Le bois donne un petit choc. L'eau se calme contre le ponton. Il ne bouge plus. Maintenant on peut descendre.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1608,7 +1656,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1684,10 +1732,30 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Léa a dit le nom du véhicule. Bateau. Avion. Train. Elle est restée avec maman.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>enfant-m|Le bateau.
+enfant-m|Le bac.
+maman|Oui, le bateau.
+narrateur|Ils restent assis sur le bord sec.
+narrateur|La maison rouge grossit.
+enfant-m|Je la vois bien.
+maman|Tu l'as voulue.
+maman|La voilà.
+narrateur|Une mouette suit le bac.
+narrateur|Son ombre passe sur l'eau.
+enfant-m|Elle vole avec nous.
+maman|Nous, on reste assis.
+maman|Merci, Victorino.
+narrateur|Le ponton de l'autre rive s'approche.
+narrateur|Une corde attend, déjà.
+enfant-m|On arrive.
+maman|On se lève avec maman.
+maman|Quand le bac est arrêté.
+narrateur|Le bois donne un petit choc.
+narrateur|L'eau se calme contre le ponton.
+enfant-m|Il ne bouge plus.
+maman|Maintenant on peut descendre.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1712,12 +1780,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le bateau s'arrête. Léa donne la main à maman. Elles descendent ensemble.</t>
+          <t>Tu donnes la main ? Oui, maman. Ils descendent ensemble. Le ponton sent encore le sel. La maison rouge. Elle est là, tout près. Victorino regarde le bac derrière lui. Le petit bateau attend déjà. On est venus en bateau. Avec un adulte. Sa chaussure laisse une trace humide. Puis le bois du ponton la boit.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le bateau s'arrête. Léa donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; à maman. Elles descendent ensemble.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Tu donnes la main ? Oui, maman. Ils descendent ensemble. Le ponton sent encore le sel. La maison rouge. Elle est là, tout près. Victorino regarde le bac derrière lui. Le petit bateau attend déjà. On est venus en bateau. Avec un adulte. Sa chaussure laisse une trace humide. Puis le bois du ponton la boit.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1780,7 +1848,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1852,10 +1920,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le bateau s'arrête. Léa donne la main à maman. Elles descendent ensemble.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>maman|Tu donnes la main ?
+enfant-m|Oui, maman.
+narrateur|Ils descendent ensemble.
+narrateur|Le ponton sent encore le sel.
+enfant-m|La maison rouge.
+maman|Elle est là, tout près.
+narrateur|Victorino regarde le bac derrière lui.
+narrateur|Le petit bateau attend déjà.
+enfant-m|On est venus en bateau.
+maman|Avec un adulte.
+narrateur|Sa chaussure laisse une trace humide.
+narrateur|Puis le bois du ponton la boit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1880,12 +1958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La maison rouge a un volet ouvert. Le bac reste collé au ponton. J'ai vu l'autre rive. Assis, avec maman. L'eau salée clapote encore, tout bas.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La maison rouge a un volet ouvert. Le bac reste collé au ponton. J'ai vu l'autre rive. Assis, avec maman. L'eau salée clapote encore, tout bas.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1941,14 +2019,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2020,10 +2098,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|La maison rouge a un volet ouvert.
+narrateur|Le bac reste collé au ponton.
+enfant-m|J'ai vu l'autre rive.
+maman|Assis, avec maman.
+narrateur|L'eau salée clapote encore, tout bas.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2042,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2080,6 +2161,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.TRA.001-02.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.001-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>port</t>
+          <t>ponton puis banc du petit bac</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Léa, maman</t>
+          <t>Victorino, maman</t>
         </is>
       </c>
     </row>
